--- a/Project 2_ Calc-o-stack.xlsx
+++ b/Project 2_ Calc-o-stack.xlsx
@@ -1,27 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <workbookPr hidePivotFieldList="1"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryanvu/Documents/Project2-TaskCalcOStack/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C416835B-63FF-1942-81AE-EFEAC25CD935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="20" yWindow="760" windowWidth="29400" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Task 1" sheetId="1" r:id="rId4"/>
+    <sheet name="Task 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
-  <si>
-    <t>Symbol</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="67">
   <si>
     <t>Stack</t>
   </si>
   <si>
-    <t>Postfix Expression</t>
-  </si>
-  <si>
     <t>a</t>
   </si>
   <si>
@@ -43,9 +59,6 @@
     <t>(</t>
   </si>
   <si>
-    <t>(/</t>
-  </si>
-  <si>
     <t>c</t>
   </si>
   <si>
@@ -55,18 +68,12 @@
     <t>-</t>
   </si>
   <si>
-    <t>(-</t>
-  </si>
-  <si>
     <t>ab*ca</t>
   </si>
   <si>
     <t>)</t>
   </si>
   <si>
-    <t>ab*ca-</t>
-  </si>
-  <si>
     <t>+</t>
   </si>
   <si>
@@ -91,23 +98,167 @@
     <t>End</t>
   </si>
   <si>
-    <t>ab*ca-/de+*</t>
+    <t>Next Character</t>
+  </si>
+  <si>
+    <t>Postfix Form</t>
+  </si>
+  <si>
+    <t>Operator Stack</t>
+  </si>
+  <si>
+    <t>a*b/(c-a)+d*e</t>
+  </si>
+  <si>
+    <t>/(</t>
+  </si>
+  <si>
+    <t>/(-</t>
+  </si>
+  <si>
+    <t>ab*ca-/de*+</t>
+  </si>
+  <si>
+    <t>Evaluation</t>
+  </si>
+  <si>
+    <t>a = 2</t>
+  </si>
+  <si>
+    <t>b = 3</t>
+  </si>
+  <si>
+    <t>c = 4</t>
+  </si>
+  <si>
+    <t>d = 5</t>
+  </si>
+  <si>
+    <t>e = 6</t>
+  </si>
+  <si>
+    <t>2 * 3</t>
+  </si>
+  <si>
+    <t>2,</t>
+  </si>
+  <si>
+    <t>2, 3</t>
+  </si>
+  <si>
+    <t>2 * 3 -&gt;</t>
+  </si>
+  <si>
+    <t>6,</t>
+  </si>
+  <si>
+    <t>a -&gt;</t>
+  </si>
+  <si>
+    <t>b -&gt;</t>
+  </si>
+  <si>
+    <t>* 3 &lt;-</t>
+  </si>
+  <si>
+    <t>c -&gt;</t>
+  </si>
+  <si>
+    <t>6, 4</t>
+  </si>
+  <si>
+    <t>6, 4, 2</t>
+  </si>
+  <si>
+    <t>- 2 &lt;-</t>
+  </si>
+  <si>
+    <t>4 - 2 &lt;-</t>
+  </si>
+  <si>
+    <t>4 - 2 -&gt;</t>
+  </si>
+  <si>
+    <t>6, 2</t>
+  </si>
+  <si>
+    <t>/ 2 &lt;-</t>
+  </si>
+  <si>
+    <t>6 / 2 &lt;-</t>
+  </si>
+  <si>
+    <t>6 / 2 -&gt;</t>
+  </si>
+  <si>
+    <t>3,</t>
+  </si>
+  <si>
+    <t>d -&gt;</t>
+  </si>
+  <si>
+    <t>3, 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e -&gt; </t>
+  </si>
+  <si>
+    <t>3, 5, 6</t>
+  </si>
+  <si>
+    <t>* 6 &lt;-</t>
+  </si>
+  <si>
+    <t>5 * 6 &lt;-</t>
+  </si>
+  <si>
+    <t>5 * 6 -&gt;</t>
+  </si>
+  <si>
+    <t>3, 30</t>
+  </si>
+  <si>
+    <t>+ 30 &lt;-</t>
+  </si>
+  <si>
+    <t>3 + 30 &lt;-</t>
+  </si>
+  <si>
+    <t>3 + 30 -&gt;</t>
+  </si>
+  <si>
+    <t>33,</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -116,54 +267,281 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <top/>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf quotePrefix="1" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{07F8B889-966D-CF49-B842-8BDBE5F1D6C3}" name="Table1" displayName="Table1" ref="F1:H27" totalsRowShown="0">
+  <autoFilter ref="F1:H27" xr:uid="{07F8B889-966D-CF49-B842-8BDBE5F1D6C3}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{52B773F4-E2F7-B243-950B-6A5E4F8292A3}" name="4"/>
+    <tableColumn id="2" xr3:uid="{B7C3D684-30CC-5A44-9AC4-6DDF1C342BE1}" name="Evaluation" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{E71038B1-FFBB-0C4D-AAA6-B80B4585AA3B}" name="Stack" dataDxfId="7"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{775A8D7C-EB45-F049-A785-A366E94A3BF8}" name="Table2" displayName="Table2" ref="A1:D15" tableBorderDxfId="6">
+  <autoFilter ref="A1:D15" xr:uid="{775A8D7C-EB45-F049-A785-A366E94A3BF8}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{34485807-34E2-BA40-90D0-71595EEE4215}" name="1" totalsRowLabel="Total"/>
+    <tableColumn id="2" xr3:uid="{FEC36461-1236-9B40-9375-106CAF4BFAC6}" name="Next Character" dataDxfId="5" totalsRowDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{0A8095D9-AB51-1C4C-9E55-115BF3EBF68E}" name="Postfix Form" dataDxfId="4" totalsRowDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{C10D4EE6-4C32-F644-BBBE-8A469B85E3CF}" name="Operator Stack" totalsRowFunction="count" dataDxfId="3" totalsRowDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -353,179 +731,388 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:H27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="15.63"/>
+    <col min="2" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="F2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="D4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="D5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="D7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="D9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="G10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="H10" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="D11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="G11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="1" t="s">
+      <c r="D12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
+      <c r="G13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="D14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="1" t="s">
-        <v>26</v>
+      <c r="C15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="G15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G16" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="2"/>
+      <c r="G17" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D19" s="7"/>
+      <c r="G19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G20" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G22" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G23" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G24" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G26" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G27" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>